--- a/data/trans_camb/IP16B08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B08-Habitat-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,95</t>
+          <t>0,0; 70,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,43</t>
+          <t>0,0; 70,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,25</t>
+          <t>0,0; 26,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,46</t>
+          <t>0,0; 26,09</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 202,59</t>
+          <t>0,0; 243,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 249,74</t>
+          <t>0,0; 238,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,6</t>
+          <t>0,0; 36,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,81</t>
+          <t>0,0; 35,3</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,56</t>
+          <t>0,0; 83,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,11</t>
+          <t>0,0; 83,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,66</t>
+          <t>0,0; 41,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,16</t>
+          <t>0,0; 46,56</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 473,31</t>
+          <t>0,0; 494,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 204,07</t>
+          <t>0,0; 494,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,04</t>
+          <t>0,0; 71,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,74</t>
+          <t>0,0; 87,12</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-70,27; 0,0</t>
+          <t>-69,56; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-43,45; 0,0</t>
+          <t>-44,5; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,27; 0,0</t>
+          <t>-69,56; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,45; 0,0</t>
+          <t>-44,5; 0,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,68</t>
+          <t>0,0; 20,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,69</t>
+          <t>0,0; 20,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 6,91</t>
+          <t>-20,88; 6,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,4</t>
+          <t>0,0; 17,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 8,72</t>
+          <t>-6,86; 9,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,05</t>
+          <t>1,51; 12,32</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,08</t>
+          <t>0,0; 26,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,09</t>
+          <t>0,0; 26,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 7,42</t>
+          <t>-21,3; 7,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,61</t>
+          <t>0,0; 20,89</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 9,68</t>
+          <t>-6,97; 10,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,54; 15,0</t>
+          <t>1,53; 14,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B08-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B08-Habitat-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,95</t>
+          <t>0,0; 70,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,45</t>
+          <t>0,0; 66,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,73</t>
+          <t>0,0; 27,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,09</t>
+          <t>0,0; 31,13</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 243,6</t>
+          <t>0,0; 236,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 238,13</t>
+          <t>0,0; 201,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,48</t>
+          <t>0,0; 37,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,3</t>
+          <t>0,0; 45,2</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,18</t>
+          <t>0,0; 67,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,18</t>
+          <t>0,0; 82,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,63</t>
+          <t>0,0; 46,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,56</t>
+          <t>0,0; 46,02</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 494,48</t>
+          <t>0,0; 204,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 494,48</t>
+          <t>0,0; 462,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,82</t>
+          <t>0,0; 86,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 87,12</t>
+          <t>0,0; 85,26</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-69,56; 0,0</t>
+          <t>-61,0; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,5; 0,0</t>
+          <t>-51,03; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,56; 0,0</t>
+          <t>-61,0; 0,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,5; 0,0</t>
+          <t>-51,03; 0,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,89</t>
+          <t>0,0; 20,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,74</t>
+          <t>0,0; 20,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 6,95</t>
+          <t>-19,6; 6,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,28</t>
+          <t>0,0; 17,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 9,44</t>
+          <t>-6,8; 9,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 12,32</t>
+          <t>1,48; 12,48</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,4</t>
+          <t>0,0; 25,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,17</t>
+          <t>0,0; 25,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 7,45</t>
+          <t>-20,91; 7,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,89</t>
+          <t>0,0; 20,81</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 10,49</t>
+          <t>-6,94; 10,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,04</t>
+          <t>1,5; 14,25</t>
         </is>
       </c>
     </row>
